--- a/Downloads/Splitflask-Financials/deliverables/CB_2025_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/CB_2025_Amendment_Packet.xlsx
@@ -758,18 +758,18 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="71" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
-      <c r="B5" s="48" t="n">
+      <c r="B5" s="64" t="n">
         <v>95558</v>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C5" s="64" t="n">
         <v>107876</v>
       </c>
-      <c r="D5" s="48" t="n">
+      <c r="D5" s="64" t="n">
         <v>12318</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1256,7 +1256,7 @@
           <t>unknown (filed Sch C needed)</t>
         </is>
       </c>
-      <c r="C32" s="52" t="n">
+      <c r="C32" s="68" t="n">
         <v>62867.23</v>
       </c>
       <c r="D32" s="19" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="72" t="inlineStr">
         <is>
           <t>REV_BNPL_CB in bank (2025)</t>
         </is>
@@ -1615,7 +1615,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>BNPL treatment</t>
         </is>
@@ -1834,12 +1834,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>TOTAL AMENDED REVENUE</t>
         </is>
       </c>
-      <c r="E11" s="48" t="n">
+      <c r="E11" s="64" t="n">
         <v>107876</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t>vs FILED gross receipts</t>
         </is>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="60" t="n">
         <v>95558</v>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
           <t>GROSS-UP NEEDED</t>
         </is>
       </c>
-      <c r="E13" s="52" t="n">
+      <c r="E13" s="68" t="n">
         <v>12318</v>
       </c>
       <c r="F13" s="9" t="inlineStr">
@@ -1957,7 +1957,7 @@
           <t>Total COGS — Cash Method</t>
         </is>
       </c>
-      <c r="B7" s="48" t="n">
+      <c r="B7" s="64" t="n">
         <v>3266.67</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>~1,400 units × $41.04. ESTIMATE — actual units × actual cost needed from Shopify sales export + Kangdao invoices.</t>
+          <t>~1,400 CB (Cyberbackpack) units × $41.04. NOTE: The 1,400 Splitflask tumbler units consigned to Atlantic Access (UK) are SPLT inventory — DIFFERENT product, DIFFERENT entity. $41.04 = Cyberbackpack cost ONLY. Tumblers = $8.11/unit landed.</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       <c r="B6" s="41" t="n">
         <v>4407.89</v>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2214,7 +2214,7 @@
       <c r="B7" s="43" t="n">
         <v>17818.73</v>
       </c>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C7" s="54" t="inlineStr">
         <is>
           <t>SOURCED-INTERCO</t>
         </is>
@@ -2239,7 +2239,7 @@
       <c r="B8" s="43" t="n">
         <v>240.47</v>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="54" t="inlineStr">
         <is>
           <t>SOURCED-INTERCO</t>
         </is>
@@ -2264,7 +2264,7 @@
       <c r="B9" s="41" t="n">
         <v>980.27</v>
       </c>
-      <c r="C9" s="42" t="inlineStr">
+      <c r="C9" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2289,7 +2289,7 @@
       <c r="B10" s="45" t="n">
         <v>1043.82</v>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2314,7 +2314,7 @@
       <c r="B11" s="41" t="n">
         <v>1336.2</v>
       </c>
-      <c r="C11" s="42" t="inlineStr">
+      <c r="C11" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2339,7 +2339,7 @@
       <c r="B12" s="41" t="n">
         <v>50</v>
       </c>
-      <c r="C12" s="42" t="inlineStr">
+      <c r="C12" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2361,10 +2361,10 @@
           <t>SUBTOTAL — Advertising</t>
         </is>
       </c>
-      <c r="B13" s="48" t="n">
+      <c r="B13" s="64" t="n">
         <v>25877.38</v>
       </c>
-      <c r="C13" s="49" t="inlineStr"/>
+      <c r="C13" s="62" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="6" t="inlineStr"/>
     </row>
@@ -2388,7 +2388,7 @@
       <c r="B15" s="45" t="n">
         <v>3266.67</v>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C15" s="66" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2424,7 +2424,7 @@
       <c r="B17" s="41" t="n">
         <v>8000</v>
       </c>
-      <c r="C17" s="42" t="inlineStr">
+      <c r="C17" s="58" t="inlineStr">
         <is>
           <t>SOURCED+VERIFIED</t>
         </is>
@@ -2460,7 +2460,7 @@
       <c r="B19" s="41" t="n">
         <v>2749.36</v>
       </c>
-      <c r="C19" s="42" t="inlineStr">
+      <c r="C19" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2485,7 +2485,7 @@
       <c r="B20" s="45" t="n">
         <v>1000</v>
       </c>
-      <c r="C20" s="46" t="inlineStr">
+      <c r="C20" s="66" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2510,7 +2510,7 @@
       <c r="B21" s="41" t="n">
         <v>603.28</v>
       </c>
-      <c r="C21" s="42" t="inlineStr">
+      <c r="C21" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2535,7 +2535,7 @@
       <c r="B22" s="41" t="n">
         <v>431.52</v>
       </c>
-      <c r="C22" s="42" t="inlineStr">
+      <c r="C22" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2560,7 +2560,7 @@
       <c r="B23" s="41" t="n">
         <v>201.62</v>
       </c>
-      <c r="C23" s="42" t="inlineStr">
+      <c r="C23" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2585,7 +2585,7 @@
       <c r="B24" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="42" t="inlineStr">
+      <c r="C24" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2610,7 +2610,7 @@
       <c r="B25" s="41" t="n">
         <v>194</v>
       </c>
-      <c r="C25" s="42" t="inlineStr">
+      <c r="C25" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2635,7 +2635,7 @@
       <c r="B26" s="41" t="n">
         <v>235.59</v>
       </c>
-      <c r="C26" s="42" t="inlineStr">
+      <c r="C26" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2660,7 +2660,7 @@
       <c r="B27" s="41" t="n">
         <v>56.54</v>
       </c>
-      <c r="C27" s="42" t="inlineStr">
+      <c r="C27" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2685,7 +2685,7 @@
       <c r="B28" s="41" t="n">
         <v>160</v>
       </c>
-      <c r="C28" s="42" t="inlineStr">
+      <c r="C28" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2710,7 +2710,7 @@
       <c r="B29" s="41" t="n">
         <v>58.76</v>
       </c>
-      <c r="C29" s="42" t="inlineStr">
+      <c r="C29" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2735,7 +2735,7 @@
       <c r="B30" s="41" t="n">
         <v>136</v>
       </c>
-      <c r="C30" s="42" t="inlineStr">
+      <c r="C30" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2760,7 +2760,7 @@
       <c r="B31" s="41" t="n">
         <v>128.05</v>
       </c>
-      <c r="C31" s="42" t="inlineStr">
+      <c r="C31" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2785,7 +2785,7 @@
       <c r="B32" s="45" t="n">
         <v>400</v>
       </c>
-      <c r="C32" s="46" t="inlineStr">
+      <c r="C32" s="66" t="inlineStr">
         <is>
           <t>FLAG-TJ</t>
         </is>
@@ -2807,10 +2807,10 @@
           <t>SUBTOTAL — OPEX</t>
         </is>
       </c>
-      <c r="B33" s="48" t="n">
+      <c r="B33" s="64" t="n">
         <v>6364.72</v>
       </c>
-      <c r="C33" s="49" t="inlineStr"/>
+      <c r="C33" s="62" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
     </row>
@@ -2834,7 +2834,7 @@
       <c r="B35" s="43" t="n">
         <v>1500</v>
       </c>
-      <c r="C35" s="44" t="inlineStr">
+      <c r="C35" s="54" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
@@ -2873,10 +2873,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B37" s="48" t="n">
+      <c r="B37" s="64" t="n">
         <v>107876</v>
       </c>
-      <c r="C37" s="49" t="inlineStr">
+      <c r="C37" s="62" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
@@ -2894,10 +2894,10 @@
           <t>NET SCHEDULE C INCOME (amended, cash COGS)</t>
         </is>
       </c>
-      <c r="B38" s="52" t="n">
+      <c r="B38" s="68" t="n">
         <v>62867.23</v>
       </c>
-      <c r="C38" s="46" t="inlineStr">
+      <c r="C38" s="66" t="inlineStr">
         <is>
           <t>PROFIT</t>
         </is>
